--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxlab\Desktop\달탐사워크숍_2026\mysite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599024F0-0957-4CDD-AD3A-1BE2BBAD0920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446590CD-055D-48F0-A880-E314CFCB4501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="105">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -133,155 +133,325 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Initial Operational Plan for LUSEM: Measuring Charged Particles on the Lunar Surface</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoMo: Decaying Orbiter of the MOon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저에너지 정전분석기 시제품 개발 현황 및 달 우주환경 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이은지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달탐사에 있어 특정지역의 고도별 정보가 중요함에도 이러한 측정자료를 얻기가 쉽지가 않다. 또한 비용대비 효과에 있어서도 어려운 기술적인 도전이다. 이에 특정지역의 고도별 자기장 및 전자기 환경 관측을 관측하기 위한 초소형 관측기기를 소개한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김관혁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IM-3 달 착륙선 탑재체 LUSEM의 과학적 목표와 관측 전망</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선종호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본 발표에서는 민간 달 착륙선 Intuitive Machines-3 (IM-3)에 탑재되어 달 표면으로 향하는 Lunar Space Environment Monitor (LUSEM)의 과학적 임무와 이를 통해 기대되는 연구 성과를 소개한다. LUSEM은 달 표면 및 주변 공간의 고에너지 입자를 관측하기 위해 개발된 탑재체로 Reiner Gamma  주변의 달 표면 우주환경을 이해하는 중요한 역할을 수행할  것으로 기대된다. 본 연구에서는 LUSEM의 개발 목적과 관측 메커니즘을 설명하고,  고에너지 입자 검출 시뮬레이션을 기반으로 도출된 초기 관측 기대 결과를 제시한다. LUSEM이 확보할 데이터는 달 표면의 전자기적 특성과 태양풍 및 지구 자기권과의 상호작용을 규명하는 데 기여할 것이며, 향후 유인 달 탐사 (아르테미스 계획 등)를 위한 우주 방사선 환경 예측 모델 수립에 필요한 기초 자료가 될 것으로 기대된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송영주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IM-5 달 착륙선용 우주 방사선 검출기인 LVRAD의 개요 (Overview of LVRAD: A Space Radiation Detector for the IM-5 Lunar Lander)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이덕행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LVRAD(Lunar Vehicle RAdiation Dosimeter)는 달 표면 방사선 환경 관측을 위해 개발된 한국천문연구원(KASI) 주도 탑재체이다. 본 탑재체는 NASA CLPS(민간 달 탑재체 서비스) 계획의 일환으로 Intuitive Machines사의 IM-5 착륙선에 탑재되어 2030년 발사될 예정이다. LVRAD의 주 임무는 달 표면의 방사선 환경을 측정하고 생물학적 영향 평가를 위한 선량 지표를 산출하는 것이며, 부차 임무로서 열 및 열외 중성자 측정을 통한 지하 얼음(물) 증거 탐색과 감마선 분광 분석을 통한 표면 방사성 물질 분석을 수행한다. 본 발표에서는 LVRAD의 과학적 임무 목적과 함께, 이를 수행하기 위한 시스템 구성 모듈 및 하드웨어 설계에 대해 소개하고자 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초청: 달 궤도선 다누리의 본체 형상 설계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신현진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 궤도선 다누리 본체 형상의 특징에 관해 소개하며, 탑재체 및 본체 구성품들의 배치에 관해 설명하고자 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lunarscience</t>
+  </si>
+  <si>
+    <t>저에너지 정전분석기 개발 현황을 공유하고, 이를 활용한 달 및 우주환경 연구의 중요성을 소개한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(가제) Landing Site Selection of Pit Craters for the Lunar Landing Mission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 항법·통신 위성군을 위한 궤도설계와 운용 전략</t>
+  </si>
+  <si>
+    <t>(presentation)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(presentor)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(abstract)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Multispacecraft observations of solar wind upstream waves near lunar orbit </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이준현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Polarization properties of Reiner Gamma Swirl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Initial Operational Plan for LUSEM: Measuring Charged Particles on the Lunar Surface</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DoMo: Decaying Orbiter of the MOon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저에너지 정전분석기 시제품 개발 현황 및 달 우주환경 연구</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Landing Site Selection of Pit Craters for the Lunar Landing Mission</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이은지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>개발 현황 공유 및 달 우주환경 연구 중요성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>달탐사에 있어 특정지역의 고도별 정보가 중요함에도 이러한 측정자료를 얻기가 쉽지가 않다. 또한 비용대비 효과에 있어서도 어려운 기술적인 도전이다. 이에 특정지역의 고도별 자기장 및 전자기 환경 관측을 관측하기 위한 초소형 관측기기를 소개한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>달 표면 대표적인 스월(lunar swirl)중 하나인 라이나 감마 스월(Reiner Gamma Swirl)을 다누리 편광관측 데이타와 아폴로 샘플 편광 실험 결과를 분석해 달 스월의 생성과정에 대해 분석한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>d2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Origin and dynamics of lunar nearside ions in Earth’s magnetotail lobes: Observations and simulations</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김관혁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Using Kaguya data, we statistically investigated the spatial distribution and dynamics of lunar ions when the Moon was in the terrestrial magnetotail lobes. These ions were observed on the dayside at altitudes of 30–120 km, with energies of ~50-1000 eV. Because they originate from neutral particles in the lunar exosphere or at the surface, their analysis provides a valuable diagnostic of the neutral particle distribution. To examine the origin and distribution of these ions, we performed test-particle simulations of lunar ions generated at the surface and in the exosphere. The results show that the spatial distribution of lunar ions observed at spacecraft altitudes is not globally uniform relative to the underlying exosphere, but is instead concentrated over the Procellarum KREEP Terrane (PKT). Both observations and simulations indicate that the PKT region serves as a major source of lunar ions at spacecraft altitudes.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IM-3 달 착륙선 탑재체 LUSEM의 과학적 목표와 관측 전망</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선종호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>본 발표에서는 민간 달 착륙선 Intuitive Machines-3 (IM-3)에 탑재되어 달 표면으로 향하는 Lunar Space Environment Monitor (LUSEM)의 과학적 임무와 이를 통해 기대되는 연구 성과를 소개한다. LUSEM은 달 표면 및 주변 공간의 고에너지 입자를 관측하기 위해 개발된 탑재체로 Reiner Gamma  주변의 달 표면 우주환경을 이해하는 중요한 역할을 수행할  것으로 기대된다. 본 연구에서는 LUSEM의 개발 목적과 관측 메커니즘을 설명하고,  고에너지 입자 검출 시뮬레이션을 기반으로 도출된 초기 관측 기대 결과를 제시한다. LUSEM이 확보할 데이터는 달 표면의 전자기적 특성과 태양풍 및 지구 자기권과의 상호작용을 규명하는 데 기여할 것이며, 향후 유인 달 탐사 (아르테미스 계획 등)를 위한 우주 방사선 환경 예측 모델 수립에 필요한 기초 자료가 될 것으로 기대된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">달 항법·통신 위성군을 위한 궤도설계와 운용 전략 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>송영주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IM-5 달 착륙선용 우주 방사선 검출기인 LVRAD의 개요 (Overview of LVRAD: A Space Radiation Detector for the IM-5 Lunar Lander)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이덕행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LVRAD(Lunar Vehicle RAdiation Dosimeter)는 달 표면 방사선 환경 관측을 위해 개발된 한국천문연구원(KASI) 주도 탑재체이다. 본 탑재체는 NASA CLPS(민간 달 탑재체 서비스) 계획의 일환으로 Intuitive Machines사의 IM-5 착륙선에 탑재되어 2030년 발사될 예정이다. LVRAD의 주 임무는 달 표면의 방사선 환경을 측정하고 생물학적 영향 평가를 위한 선량 지표를 산출하는 것이며, 부차 임무로서 열 및 열외 중성자 측정을 통한 지하 얼음(물) 증거 탐색과 감마선 분광 분석을 통한 표면 방사성 물질 분석을 수행한다. 본 발표에서는 LVRAD의 과학적 임무 목적과 함께, 이를 수행하기 위한 시스템 구성 모듈 및 하드웨어 설계에 대해 소개하고자 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:00</t>
+  </si>
+  <si>
+    <t>박현후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조우인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤동석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김상화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">초청: </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invited</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -669,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
@@ -721,22 +891,22 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -750,22 +920,22 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -779,16 +949,16 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
         <v>20</v>
@@ -805,27 +975,27 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -834,133 +1004,486 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>88</v>
+      </c>
+      <c r="I9" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" t="s">
+        <v>99</v>
+      </c>
+      <c r="I18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" t="s">
+        <v>100</v>
+      </c>
+      <c r="I19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" t="s">
-        <v>48</v>
-      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" t="s">
+        <v>65</v>
+      </c>
+      <c r="I22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="1"/>
+      <c r="E23"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C24" s="1"/>
+      <c r="E24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxlab\Desktop\달탐사워크숍_2026\mysite\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446590CD-055D-48F0-A880-E314CFCB4501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{446590CD-055D-48F0-A880-E314CFCB4501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53999AAF-FD5D-438C-A0DB-A2A7DD9A230B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="103">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -249,10 +249,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>s13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s14</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -293,10 +289,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>초청: 달 궤도선 다누리의 본체 형상 설계</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -309,10 +301,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>s21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>13:40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -365,14 +353,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>17:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>lunarscience</t>
   </si>
   <si>
@@ -435,10 +415,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>학생1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>학생2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -447,11 +423,51 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">초청: </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Invited</t>
+    <t>홍예원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Some lunar crustal magnetic anomalies are associated with albedo markings known as swirls; however, the processes governing their formation remain unclear. In this study, we focus on Reiner Gamma, a well-studied lunar anomaly and a key site for investigating the relationship between albedo patterns and magnetic anomalies. We perform test-particle simulations to examine how the Reiner Gamma swirl interacts with the local magnetic field, employing incident solar wind particles with energies of 0.5–1.0 keV and both line and disk magnetization models. The simulated magnetic fields are comparable to observations from previous lunar orbiters at altitudes of approximately 20 km and 40 km. Their maximum and minimum intensities, corresponding respectively to bright lobes and dark cusps on the lunar surface, align with the optical albedo patterns observed at Reiner Gamma. Our simulations show that the reflection area of solar wind particles above Reiner Gamma increases as the incident solar wind energy decreases. In the bright lobes, solar wind particle reflection exhibits a clear dependence on strong horizontal magnetic fields and dominant perpendicular energies. In contrast, reflection in the cusps is less definitive, being additionally governed by the interplay between relative perpendicular energy and magnetic configuration. We discuss the necessary conditions under which incident solar wind particles are absorbed at the surface or reflected above Reiner Gamma.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interaction Between Solar Wind Particles and the Reiner Gamma Magnetic Anomaly: Observations and Test-Particle Simulations</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Observational and Simulation Insights into Lunar-Origin Ion Acceleration in Earth’s
+Magnetotail Lobes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Kaguya observed rapid energy fluctuations, varying by a factor of ~10 within a few minutes, during passages near the subsolar region (SEL latitude -30° to 40°, longitude -5° to 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>°</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) at altitudes of 50 and 100 km in the Earth’s magnetotail lobes. Lunar-origin ions near the lunar surface and in the exosphere are known to be accelerated by two electric fields: the near- surface photoelectron sheath field and the tail lobe convection field. To interpret the Kaguya observations, test-particle simulations were performed using representative surface potentials and lobe convection velocities. The simulations indicate that large energy variations of lunar-origin ions observed by Kaguya cannot be explained solely by the combined effects of photoelectric and motional electric fields, suggesting the presence of additional acceleration mechanisms</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -459,7 +475,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,6 +490,13 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -498,11 +521,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -839,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
@@ -891,10 +917,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -920,10 +946,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -949,10 +975,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -975,10 +1001,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -1007,7 +1033,7 @@
         <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1019,7 +1045,7 @@
         <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1033,16 +1059,16 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s">
         <v>26</v>
@@ -1059,16 +1085,16 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s">
         <v>37</v>
@@ -1085,22 +1111,22 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1114,19 +1140,19 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1140,22 +1166,22 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F11" t="s">
-        <v>83</v>
-      </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1169,22 +1195,22 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s">
         <v>31</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1198,22 +1224,22 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="H13" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1221,28 +1247,28 @@
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
         <v>82</v>
       </c>
-      <c r="F14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" t="s">
-        <v>87</v>
-      </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1256,22 +1282,22 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1285,22 +1311,22 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
       </c>
-      <c r="G16" t="s">
-        <v>87</v>
+      <c r="G16" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I16" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1314,22 +1340,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1343,22 +1369,22 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
-      <c r="G18" t="s">
-        <v>87</v>
+      <c r="G18" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="H18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1372,22 +1398,22 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1401,89 +1427,31 @@
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>61</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I20" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" t="s">
-        <v>89</v>
-      </c>
+      <c r="C21" s="1"/>
+      <c r="E21"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" t="s">
-        <v>65</v>
-      </c>
-      <c r="I22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="1"/>
-      <c r="E23"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="1"/>
-      <c r="E24"/>
+      <c r="C22" s="1"/>
+      <c r="E22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{446590CD-055D-48F0-A880-E314CFCB4501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53999AAF-FD5D-438C-A0DB-A2A7DD9A230B}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{446590CD-055D-48F0-A880-E314CFCB4501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F0CCDA6-DD0E-4D34-9480-85F32DFF1BE4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="975" yWindow="0" windowWidth="28350" windowHeight="15585" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="100">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -245,10 +245,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>s12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s14</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -333,14 +329,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>16:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -360,18 +348,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(가제) Landing Site Selection of Pit Craters for the Lunar Landing Mission</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>달 항법·통신 위성군을 위한 궤도설계와 운용 전략</t>
   </si>
   <si>
     <t>(presentation)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(presentor)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -468,6 +448,14 @@
   </si>
   <si>
     <t>17:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Landing Site Selection of Pit Craters for the Lunar Landing Mission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:05</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -521,14 +509,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -546,6 +531,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -865,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
@@ -917,10 +906,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -946,10 +935,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -975,10 +964,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -1001,10 +990,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -1033,7 +1022,7 @@
         <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1045,7 +1034,7 @@
         <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1059,16 +1048,16 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H7" t="s">
         <v>26</v>
@@ -1085,16 +1074,16 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H8" t="s">
         <v>37</v>
@@ -1111,22 +1100,22 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H9" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1140,19 +1129,19 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" t="s">
         <v>75</v>
       </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1166,22 +1155,22 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" t="s">
-        <v>78</v>
-      </c>
       <c r="G11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1195,22 +1184,22 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s">
         <v>31</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1218,28 +1207,28 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
         <v>78</v>
       </c>
-      <c r="G13" t="s">
-        <v>62</v>
-      </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1253,22 +1242,22 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I14" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1282,22 +1271,22 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1311,22 +1300,22 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>100</v>
+      <c r="G16" t="s">
+        <v>78</v>
       </c>
       <c r="H16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1340,22 +1329,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1369,22 +1358,22 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>99</v>
+        <v>16</v>
+      </c>
+      <c r="G18" t="s">
+        <v>78</v>
       </c>
       <c r="H18" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1398,60 +1387,31 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" t="s">
-        <v>96</v>
-      </c>
-      <c r="I20" t="s">
-        <v>84</v>
-      </c>
+      <c r="C20" s="1"/>
+      <c r="E20"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C21" s="1"/>
       <c r="E21"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="1"/>
-      <c r="E22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{446590CD-055D-48F0-A880-E314CFCB4501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F0CCDA6-DD0E-4D34-9480-85F32DFF1BE4}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{446590CD-055D-48F0-A880-E314CFCB4501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E371706-1DA1-4BEB-8128-0439541C9848}"/>
   <bookViews>
-    <workbookView xWindow="975" yWindow="0" windowWidth="28350" windowHeight="15585" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="0" yWindow="3525" windowWidth="28350" windowHeight="11295" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="103">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -245,6 +245,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>s12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>s14</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -329,6 +333,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>16:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>16:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -352,6 +364,10 @@
   </si>
   <si>
     <t>(presentation)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(presentor)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -452,10 +468,6 @@
   </si>
   <si>
     <t>Landing Site Selection of Pit Craters for the Lunar Landing Mission</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:05</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -531,10 +543,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -854,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
@@ -906,10 +914,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -935,10 +943,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -964,10 +972,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -990,10 +998,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -1022,7 +1030,7 @@
         <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1034,7 +1042,7 @@
         <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1048,16 +1056,16 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H7" t="s">
         <v>26</v>
@@ -1074,16 +1082,16 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s">
         <v>37</v>
@@ -1100,22 +1108,22 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="I9" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1129,19 +1137,19 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1155,22 +1163,22 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1184,22 +1192,22 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s">
         <v>31</v>
       </c>
       <c r="I12" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1207,28 +1215,28 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1242,22 +1250,22 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1271,22 +1279,22 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1300,22 +1308,22 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="H16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1329,22 +1337,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1358,22 +1366,22 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1387,31 +1395,60 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>60</v>
       </c>
       <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" t="s">
         <v>17</v>
       </c>
-      <c r="G19" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" t="s">
-        <v>91</v>
-      </c>
-      <c r="I19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="1"/>
-      <c r="E20"/>
+      <c r="G20" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C21" s="1"/>
       <c r="E21"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="1"/>
+      <c r="E22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{446590CD-055D-48F0-A880-E314CFCB4501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E371706-1DA1-4BEB-8128-0439541C9848}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{446590CD-055D-48F0-A880-E314CFCB4501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51A1EC3B-D776-4504-BB36-91EDEB94921F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3525" windowWidth="28350" windowHeight="11295" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="29400" yWindow="1860" windowWidth="24225" windowHeight="13755" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="105">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -337,22 +337,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>lunarscience</t>
   </si>
   <si>
@@ -364,10 +348,6 @@
   </si>
   <si>
     <t>(presentation)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(presentor)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -468,6 +448,34 @@
   </si>
   <si>
     <t>Landing Site Selection of Pit Craters for the Lunar Landing Mission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김세린</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 토양의 입자 크기에 따른 편광 특성 실험 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 토양의 입자 크기와 최대 편광도 간의 관계를 조사하기 위해 입도별 아폴로 샘플의 선형 편광도를 측정하였다. 실험 결과, 입자 크기가 증가함에 따라 최대 편광도가 증가하는 경향이 나타났다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -543,6 +551,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1042,7 +1054,7 @@
         <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1065,7 +1077,7 @@
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H7" t="s">
         <v>26</v>
@@ -1091,7 +1103,7 @@
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s">
         <v>37</v>
@@ -1114,16 +1126,16 @@
         <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1137,19 +1149,19 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1163,22 +1175,22 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1192,22 +1204,22 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s">
         <v>31</v>
       </c>
       <c r="I12" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1221,22 +1233,22 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="I13" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1259,13 +1271,13 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1288,13 +1300,13 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1317,13 +1329,13 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H16" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1346,13 +1358,13 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1375,13 +1387,13 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1404,13 +1416,13 @@
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1433,13 +1445,13 @@
         <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{446590CD-055D-48F0-A880-E314CFCB4501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51A1EC3B-D776-4504-BB36-91EDEB94921F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="1860" windowWidth="24225" windowHeight="13755" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="2955" yWindow="900" windowWidth="24225" windowHeight="13755" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="99">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -209,34 +209,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>15:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10:00</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -265,30 +241,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>s18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>11:15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>초청: 달 궤도선 다누리의 본체 형상 설계</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -301,42 +257,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13:40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13:55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>14:10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14:25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>15:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>15:45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>lunarscience</t>
   </si>
   <si>
@@ -388,14 +316,6 @@
   </si>
   <si>
     <t>김상화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>학생2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>학생3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -443,10 +363,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>17:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Landing Site Selection of Pit Craters for the Lunar Landing Mission</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -459,23 +375,83 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>16:50</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>17:05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>달 토양의 입자 크기와 최대 편광도 간의 관계를 조사하기 위해 입도별 아폴로 샘플의 선형 편광도를 측정하였다. 실험 결과, 입자 크기가 증가함에 따라 최대 편광도가 증가하는 경향이 나타났다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:35</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -551,10 +527,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -926,22 +898,22 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -955,22 +927,19 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -984,19 +953,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -1010,56 +982,27 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -1068,24 +1011,27 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>52</v>
+      </c>
+      <c r="I7" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1094,16 +1040,16 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="H8" t="s">
         <v>37</v>
@@ -1111,7 +1057,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -1120,53 +1066,27 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="I9" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H10" t="s">
-        <v>80</v>
-      </c>
-    </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -1175,27 +1095,24 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -1204,27 +1121,27 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -1233,56 +1150,27 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="H13" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
@@ -1291,27 +1179,27 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
@@ -1320,27 +1208,27 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="H16" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="I16" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
@@ -1349,27 +1237,27 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="H17" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
         <v>29</v>
@@ -1378,56 +1266,27 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="H18" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="I18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
@@ -1436,31 +1295,81 @@
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="H20" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="1"/>
-      <c r="E21"/>
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="1"/>
-      <c r="E22"/>
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I22" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24A1F6A3-086A-47C5-89F6-4E2D7836FC40}"/>
   <bookViews>
     <workbookView xWindow="2955" yWindow="900" windowWidth="24225" windowHeight="13755" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="99">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1080,9 +1080,6 @@
       <c r="H9" t="s">
         <v>26</v>
       </c>
-      <c r="I9" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24A1F6A3-086A-47C5-89F6-4E2D7836FC40}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{514E9DE3-0AA2-4FA7-B75B-EE76D4323779}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="900" windowWidth="24225" windowHeight="13755" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="180" yWindow="1170" windowWidth="24225" windowHeight="13755" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -241,10 +241,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>초청: 달 궤도선 다누리의 본체 형상 설계</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -399,10 +395,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>13:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -443,15 +435,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10:35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:35</t>
+    <t>10:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -527,6 +527,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -898,10 +902,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -927,10 +931,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -953,10 +957,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -982,10 +986,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -997,7 +1001,7 @@
         <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1011,22 +1015,22 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" t="s">
         <v>51</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>52</v>
-      </c>
-      <c r="I7" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1040,16 +1044,16 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
         <v>37</v>
@@ -1066,16 +1070,16 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
         <v>26</v>
@@ -1092,19 +1096,19 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
       </c>
       <c r="G11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" t="s">
         <v>61</v>
-      </c>
-      <c r="H11" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1118,22 +1122,22 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1147,22 +1151,22 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1176,22 +1180,22 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I15" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1205,27 +1209,27 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I16" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
@@ -1234,7 +1238,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>42</v>
@@ -1243,42 +1247,42 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" t="s">
         <v>59</v>
-      </c>
-      <c r="H17" t="s">
-        <v>68</v>
-      </c>
-      <c r="I17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" t="s">
-        <v>70</v>
-      </c>
-      <c r="I18" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1292,22 +1296,22 @@
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H20" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1321,22 +1325,22 @@
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="F21" t="s">
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="H21" t="s">
         <v>69</v>
       </c>
       <c r="I21" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1350,22 +1354,22 @@
         <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="H22" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{514E9DE3-0AA2-4FA7-B75B-EE76D4323779}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A793CD0-F78B-4A1A-A625-A55312B99B34}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="1170" windowWidth="24225" windowHeight="13755" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
@@ -439,19 +439,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11:30</t>
+    <t>10:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:35</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A793CD0-F78B-4A1A-A625-A55312B99B34}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF725F56-2EB2-4033-80CA-D9D865BF833F}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="1170" windowWidth="24225" windowHeight="13755" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="9240" yWindow="0" windowWidth="18675" windowHeight="15585" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="107">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -117,22 +117,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>백슬민</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설우형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>진호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정민섭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Initial Operational Plan for LUSEM: Measuring Charged Particles on the Lunar Surface</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -145,10 +129,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이은지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -165,10 +145,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김관혁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,10 +153,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>선종호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>본 발표에서는 민간 달 착륙선 Intuitive Machines-3 (IM-3)에 탑재되어 달 표면으로 향하는 Lunar Space Environment Monitor (LUSEM)의 과학적 임무와 이를 통해 기대되는 연구 성과를 소개한다. LUSEM은 달 표면 및 주변 공간의 고에너지 입자를 관측하기 위해 개발된 탑재체로 Reiner Gamma  주변의 달 표면 우주환경을 이해하는 중요한 역할을 수행할  것으로 기대된다. 본 연구에서는 LUSEM의 개발 목적과 관측 메커니즘을 설명하고,  고에너지 입자 검출 시뮬레이션을 기반으로 도출된 초기 관측 기대 결과를 제시한다. LUSEM이 확보할 데이터는 달 표면의 전자기적 특성과 태양풍 및 지구 자기권과의 상호작용을 규명하는 데 기여할 것이며, 향후 유인 달 탐사 (아르테미스 계획 등)를 위한 우주 방사선 환경 예측 모델 수립에 필요한 기초 자료가 될 것으로 기대된다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -189,10 +161,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>송영주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -201,10 +169,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이덕행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LVRAD(Lunar Vehicle RAdiation Dosimeter)는 달 표면 방사선 환경 관측을 위해 개발된 한국천문연구원(KASI) 주도 탑재체이다. 본 탑재체는 NASA CLPS(민간 달 탑재체 서비스) 계획의 일환으로 Intuitive Machines사의 IM-5 착륙선에 탑재되어 2030년 발사될 예정이다. LVRAD의 주 임무는 달 표면의 방사선 환경을 측정하고 생물학적 영향 평가를 위한 선량 지표를 산출하는 것이며, 부차 임무로서 열 및 열외 중성자 측정을 통한 지하 얼음(물) 증거 탐색과 감마선 분광 분석을 통한 표면 방사성 물질 분석을 수행한다. 본 발표에서는 LVRAD의 과학적 임무 목적과 함께, 이를 수행하기 위한 시스템 구성 모듈 및 하드웨어 설계에 대해 소개하고자 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -245,22 +209,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>신현진</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>달 궤도선 다누리 본체 형상의 특징에 관해 소개하며, 탑재체 및 본체 구성품들의 배치에 관해 설명하고자 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>lunarscience</t>
   </si>
   <si>
@@ -283,10 +235,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이준현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Polarization properties of Reiner Gamma Swirl</t>
   </si>
   <si>
@@ -297,26 +245,6 @@
   </si>
   <si>
     <t>Using Kaguya data, we statistically investigated the spatial distribution and dynamics of lunar ions when the Moon was in the terrestrial magnetotail lobes. These ions were observed on the dayside at altitudes of 30–120 km, with energies of ~50-1000 eV. Because they originate from neutral particles in the lunar exosphere or at the surface, their analysis provides a valuable diagnostic of the neutral particle distribution. To examine the origin and distribution of these ions, we performed test-particle simulations of lunar ions generated at the surface and in the exosphere. The results show that the spatial distribution of lunar ions observed at spacecraft altitudes is not globally uniform relative to the underlying exosphere, but is instead concentrated over the Procellarum KREEP Terrane (PKT). Both observations and simulations indicate that the PKT region serves as a major source of lunar ions at spacecraft altitudes.</t>
-  </si>
-  <si>
-    <t>박현후</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조우인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>윤동석</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김상화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>홍예원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Some lunar crustal magnetic anomalies are associated with albedo markings known as swirls; however, the processes governing their formation remain unclear. In this study, we focus on Reiner Gamma, a well-studied lunar anomaly and a key site for investigating the relationship between albedo patterns and magnetic anomalies. We perform test-particle simulations to examine how the Reiner Gamma swirl interacts with the local magnetic field, employing incident solar wind particles with energies of 0.5–1.0 keV and both line and disk magnetization models. The simulated magnetic fields are comparable to observations from previous lunar orbiters at altitudes of approximately 20 km and 40 km. Their maximum and minimum intensities, corresponding respectively to bright lobes and dark cusps on the lunar surface, align with the optical albedo patterns observed at Reiner Gamma. Our simulations show that the reflection area of solar wind particles above Reiner Gamma increases as the incident solar wind energy decreases. In the bright lobes, solar wind particle reflection exhibits a clear dependence on strong horizontal magnetic fields and dominant perpendicular energies. In contrast, reflection in the cusps is less definitive, being additionally governed by the interplay between relative perpendicular energy and magnetic configuration. We discuss the necessary conditions under which incident solar wind particles are absorbed at the surface or reflected above Reiner Gamma.</t>
@@ -363,10 +291,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김세린</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>달 토양의 입자 크기에 따른 편광 특성 실험 연구</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -395,34 +319,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>16:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -452,6 +348,140 @@
   </si>
   <si>
     <t>11:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 탐사용 자기장 측정기 개발 현황</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 자기장 관측은 달 내부 구조, 자기이상지역의 기원, 태양풍과 달 표면의 상호작용을 이해하기 위한 핵심 기술이다. 경희대학교는 국내 최초의 달 탐사선 다누리 (KPLO)에 탑재된 자기장 측정기 (KMAG)를 개발하여 성공적인 달 궤도 자기장 관측을 수행하였으며, 획득된 자료를 기반으로 달 자기장 지도 구축과 다양한 과학 연구를 수행하고 있다. 또한 NASA CLPS (Commercial Lunar Payload Services) 미션을 위한 후보 탑재체로써 달 착륙선용 자기장 측정기를 개발하여 착륙 지점의 국소 자기장 및 우주환경 측정을 위한 기반 기술을 확보하였다. 현재는 향후 유인 달 탐사를 위한 달 표면 전개형 자기장 측정기를 개발하고 있다. 본 발표에서는 다누리 궤도선 자기장 측정기와 CLPS 달 착륙선 자기장 측정기의 개발 과정 및 운용 현황과 유인 우주탐사를 위한 자기장 측정기 개발 현황에 대해 소개한다.</t>
+  </si>
+  <si>
+    <t>달 표면에서의 자기장 측정은 Apollo 시대 LSM으로 시작되어 오랜 공백을 거쳐 Blue Ghost LMS 임무로 다시 이어지고 있다. 본 발표에서는 지금까지의 달 표면 자기장 미션들을 소개하고, 이 데이터들을 활용해 현재 진행 중인 연구 내용을 공유한다. 아울러 이를 바탕으로 향후 달 자기장 탐사에 있어 표면-궤도 동시 관측 및 다지점 표면 관측의 필요성을 논의한다.</t>
+  </si>
+  <si>
+    <t>달 표면 자기장 탐사 및 과학적 연구: Apollo LSM에서 Blue Ghost LMS까지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다 탑재체 데이터 활용 착륙지 안전도 사전 분석 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선종호 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설우형 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이덕행 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백슬민 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박필재 (한국전자통신연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송영주 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이은지 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이준현 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김세린 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정민섭 (한국천문연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김관혁 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤동석 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍예원 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박현후 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조우인 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김상화 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진호 (경희대학교)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신현진 (한국항공우주연구원)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -850,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
@@ -902,22 +932,22 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -931,19 +961,19 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -957,22 +987,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -986,27 +1016,27 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -1015,27 +1045,27 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1044,24 +1074,24 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -1070,50 +1100,50 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" t="s">
-        <v>61</v>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -1122,27 +1152,24 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -1151,229 +1178,259 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="I13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" t="s">
-        <v>65</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="H16" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="H17" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="I17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" t="s">
         <v>15</v>
       </c>
-      <c r="G19" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" t="s">
-        <v>66</v>
-      </c>
-      <c r="I19" t="s">
-        <v>59</v>
+      <c r="G18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H20" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="I20" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="F21" t="s">
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="I21" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" t="s">
         <v>16</v>
       </c>
-      <c r="G22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" t="s">
-        <v>28</v>
+      <c r="G23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF725F56-2EB2-4033-80CA-D9D865BF833F}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84735C57-D605-4C66-B9B4-1DC876C996E7}"/>
   <bookViews>
-    <workbookView xWindow="9240" yWindow="0" windowWidth="18675" windowHeight="15585" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="5808" yWindow="612" windowWidth="16620" windowHeight="11520" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="111">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -331,10 +331,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10:35</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -377,42 +373,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13:40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>선종호 (경희대학교)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -482,6 +442,62 @@
   </si>
   <si>
     <t>신현진 (한국항공우주연구원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초청: 달탐사 계획과 추진 방향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박진혜 (우주항공청)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:55</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -880,16 +896,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="19.375" customWidth="1"/>
-    <col min="7" max="7" width="59.125" customWidth="1"/>
-    <col min="8" max="8" width="15.875" customWidth="1"/>
+    <col min="6" max="6" width="19.3984375" customWidth="1"/>
+    <col min="7" max="7" width="59.09765625" customWidth="1"/>
+    <col min="8" max="8" width="15.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -921,7 +937,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -932,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -944,13 +960,13 @@
         <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -961,10 +977,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -973,10 +989,10 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -987,10 +1003,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -999,13 +1015,13 @@
         <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1016,10 +1032,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -1028,13 +1044,13 @@
         <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -1045,25 +1061,22 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1074,22 +1087,22 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1100,22 +1113,25 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="I9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1126,22 +1142,22 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="H10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1164,10 +1180,10 @@
         <v>48</v>
       </c>
       <c r="H12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1190,13 +1206,13 @@
         <v>58</v>
       </c>
       <c r="H13" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1219,13 +1235,13 @@
         <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1248,13 +1264,13 @@
         <v>51</v>
       </c>
       <c r="H16" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -1277,13 +1293,13 @@
         <v>55</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1306,42 +1322,39 @@
         <v>54</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
         <v>38</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" t="s">
-        <v>102</v>
-      </c>
-      <c r="I20" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1352,25 +1365,25 @@
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="H21" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1381,27 +1394,27 @@
         <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="F22" t="s">
         <v>15</v>
       </c>
       <c r="G22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
         <v>76</v>
-      </c>
-      <c r="H22" t="s">
-        <v>104</v>
-      </c>
-      <c r="I22" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>77</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -1410,21 +1423,50 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="F23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" t="s">
         <v>16</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G24" t="s">
         <v>20</v>
       </c>
-      <c r="H23" t="s">
-        <v>105</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="H24" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" t="s">
         <v>23</v>
       </c>
     </row>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84735C57-D605-4C66-B9B4-1DC876C996E7}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD00667B-25EA-4F92-9C5C-23DC6F7E41BD}"/>
   <bookViews>
-    <workbookView xWindow="5808" yWindow="612" windowWidth="16620" windowHeight="11520" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="-2616" yWindow="1020" windowWidth="16620" windowHeight="11520" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,10 +121,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DoMo: Decaying Orbiter of the MOon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>저에너지 정전분석기 시제품 개발 현황 및 달 우주환경 연구</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -498,6 +494,10 @@
   </si>
   <si>
     <t>11:55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 탐사용 초소형관측기기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -948,22 +948,22 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" t="s">
         <v>27</v>
-      </c>
-      <c r="H2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
@@ -977,10 +977,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -989,7 +989,7 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
@@ -1003,22 +1003,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" t="s">
         <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
@@ -1032,27 +1032,27 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -1061,24 +1061,24 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1087,24 +1087,24 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -1113,27 +1113,27 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
         <v>41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>96</v>
-      </c>
-      <c r="I9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -1142,24 +1142,24 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H10" t="s">
         <v>108</v>
-      </c>
-      <c r="H10" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -1168,24 +1168,24 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
@@ -1194,27 +1194,27 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -1223,251 +1223,251 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" t="s">
         <v>49</v>
-      </c>
-      <c r="H14" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" t="s">
         <v>51</v>
-      </c>
-      <c r="H16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" t="s">
         <v>55</v>
-      </c>
-      <c r="H17" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F19" t="s">
         <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" t="s">
         <v>72</v>
-      </c>
-      <c r="H21" t="s">
-        <v>92</v>
-      </c>
-      <c r="I21" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="F22" t="s">
         <v>15</v>
       </c>
       <c r="G22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" t="s">
+        <v>92</v>
+      </c>
+      <c r="I22" t="s">
         <v>46</v>
-      </c>
-      <c r="H22" t="s">
-        <v>93</v>
-      </c>
-      <c r="I22" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
         <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="H24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD00667B-25EA-4F92-9C5C-23DC6F7E41BD}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{735E7C6B-2FD3-4EBB-A040-95FF30FEE783}"/>
   <bookViews>
-    <workbookView xWindow="-2616" yWindow="1020" windowWidth="16620" windowHeight="11520" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="-540" yWindow="696" windowWidth="20484" windowHeight="11520" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="115">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -217,14 +217,6 @@
   </si>
   <si>
     <t>달 항법·통신 위성군을 위한 궤도설계와 운용 전략</t>
-  </si>
-  <si>
-    <t>(presentation)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(abstract)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Multispacecraft observations of solar wind upstream waves near lunar orbit </t>
@@ -291,10 +283,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>달 토양의 입자 크기와 최대 편광도 간의 관계를 조사하기 위해 입도별 아폴로 샘플의 선형 편광도를 측정하였다. 실험 결과, 입자 크기가 증가함에 따라 최대 편광도가 증가하는 경향이 나타났다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -303,46 +291,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>09:00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09:40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>16:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>17:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>17:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10:35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10:55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>11:15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11:35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>달 탐사용 자기장 측정기 개발 현황</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -361,10 +321,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>16:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>다 탑재체 데이터 활용 착륙지 안전도 사전 분석 방법</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -441,22 +397,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>13:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>14:30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -465,22 +409,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>15:05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15:25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>15:45</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s19</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -493,11 +425,95 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11:55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>달 탐사용 초소형관측기기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양륜관 (KAIST)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ELFO-CFO Hybrid Constellation Design for Global Lunar PNT Including Powered Descent </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다누리 자기장 측정기 KMAG를 이용한 달 내부 구조 연구</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -896,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
@@ -948,10 +964,10 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -960,7 +976,7 @@
         <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
         <v>27</v>
@@ -977,10 +993,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -989,7 +1005,7 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
@@ -1003,10 +1019,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -1015,38 +1031,38 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="I4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="H5" t="s">
-        <v>81</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="H6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1061,19 +1077,19 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
@@ -1087,53 +1103,24 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -1142,19 +1129,51 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H10" t="s">
-        <v>108</v>
+        <v>104</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
@@ -1168,53 +1187,24 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" t="s">
-        <v>86</v>
-      </c>
-      <c r="I13" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -1223,22 +1213,48 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
-      </c>
-      <c r="I14" t="s">
-        <v>49</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
@@ -1246,62 +1262,33 @@
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
         <v>42</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
@@ -1310,27 +1297,27 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I18" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
@@ -1339,19 +1326,51 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H19" t="s">
-        <v>83</v>
+        <v>78</v>
+      </c>
+      <c r="I19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
@@ -1365,56 +1384,24 @@
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="H21" t="s">
-        <v>91</v>
-      </c>
-      <c r="I21" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" t="s">
-        <v>92</v>
-      </c>
-      <c r="I22" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
@@ -1423,27 +1410,27 @@
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="H23" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -1452,21 +1439,76 @@
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
+        <v>114</v>
+      </c>
+      <c r="H24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>64</v>
+      </c>
+      <c r="H25" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" t="s">
         <v>16</v>
       </c>
-      <c r="G24" t="s">
-        <v>110</v>
-      </c>
-      <c r="H24" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="G26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s">
+        <v>83</v>
+      </c>
+      <c r="I26" t="s">
         <v>22</v>
       </c>
     </row>

--- a/2026_Lunarworkshop_presentation.xlsx
+++ b/2026_Lunarworkshop_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{735E7C6B-2FD3-4EBB-A040-95FF30FEE783}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="8_{48C49700-4057-4E5A-A4EA-ECE4EC1E6A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2354DEE9-B2FF-476D-8764-403D66235F82}"/>
   <bookViews>
-    <workbookView xWindow="-540" yWindow="696" windowWidth="20484" windowHeight="11520" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B401C6F-0E91-4446-959D-BA9485E5D47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="116">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -121,10 +121,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>저에너지 정전분석기 시제품 개발 현황 및 달 우주환경 연구</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>s5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -205,15 +201,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>달 궤도선 다누리 본체 형상의 특징에 관해 소개하며, 탑재체 및 본체 구성품들의 배치에 관해 설명하고자 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>lunarscience</t>
-  </si>
-  <si>
-    <t>저에너지 정전분석기 개발 현황을 공유하고, 이를 활용한 달 및 우주환경 연구의 중요성을 소개한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>달 항법·통신 위성군을 위한 궤도설계와 운용 전략</t>
@@ -514,6 +502,22 @@
   </si>
   <si>
     <t>다누리 자기장 측정기 KMAG를 이용한 달 내부 구조 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다누리가 달 궤도 상에서 성공적으로 과학 임무를 수행하고 있다. 이러한 임무를 수행하기 위해 고려된 기계적인 형상에 대한 특징을 소개하며, 각 탑재체의 배치에 대한 개념도 소개하고자 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 탐사 착륙지 선정에 있어서 과학탐사 목표와 함께 고려 하여야하는 착륙지 안전도 분석에 대하여 논의한다. 착륙지의 안전도 분석을 위한 수학적 틀을 제시하고 다중 탑재체 데이터 활용 방법을 모색한다. 이를 위한 탑재체 LRO - NAC, LOLA, SLDEM, Diviner, miniRF 데이터를 고려하였다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달 우주환경 관측을 위한 저에너지 정전기 분석기(ESA) 기술 개발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>본 연구에서는 차세대 우주탐사를 위한 저에너지 정전기 분석기(ESA) 기술 개발 현황을 소개한다. ESA는 수십 eV에서 수십 keV 범위의 저에너지 하전입자를 측정하여 달 주변 플라즈마 및 우주환경을 연구하는 핵심 장비이다. 한국천문연구원에서는 ESA의 국내 개발을 위해 핵심 기술을 확보하고 시제품 제작 및 성능 검증을 수행하고 있으며, 향후 달 및 행성 탐사 임무 적용을 위한 기술 기반 구축을 목표로 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -545,12 +549,18 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -567,11 +577,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -913,15 +926,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAA5805-02C0-4AE9-B5DF-E91EE7468B4D}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="19.3984375" customWidth="1"/>
-    <col min="7" max="7" width="59.09765625" customWidth="1"/>
-    <col min="8" max="8" width="15.8984375" customWidth="1"/>
+    <col min="6" max="6" width="19.375" customWidth="1"/>
+    <col min="7" max="7" width="59.125" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -953,7 +966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -964,25 +977,25 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -993,10 +1006,10 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -1005,10 +1018,10 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1019,25 +1032,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1048,27 +1061,27 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>20</v>
-      </c>
-      <c r="H6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -1077,24 +1090,24 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1103,24 +1116,27 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="G8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -1129,27 +1145,24 @@
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H10" t="s">
-        <v>104</v>
-      </c>
-      <c r="I10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -1158,27 +1171,27 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
       </c>
-      <c r="G11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" t="s">
-        <v>84</v>
+      <c r="G11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -1187,24 +1200,24 @@
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -1213,24 +1226,24 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -1239,27 +1252,27 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -1268,248 +1281,248 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s">
         <v>46</v>
       </c>
-      <c r="H16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>65</v>
-      </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H25" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
